--- a/xlsx/HerbalNames.xlsx
+++ b/xlsx/HerbalNames.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hadle\Documents\GitHub\voynichTEI\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31480247-9C5D-4D47-97D9-142C60AE68A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8854C489-692C-49B4-850C-4C0FC1BCDEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{E74B4125-5874-4082-9055-372A93C35FC0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E74B4125-5874-4082-9055-372A93C35FC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>kcho</t>
   </si>
@@ -185,10 +185,13 @@
     <t>Alkanet, bugloss</t>
   </si>
   <si>
-    <t>[&gt;\.,]</t>
-  </si>
-  <si>
-    <t>[\,\.&lt;]</t>
+    <t>Page</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
 </sst>
 </file>
@@ -567,6 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B424477-3632-40C3-B940-3D2816A9B032}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -583,6 +587,15 @@
       <c r="B1" t="s">
         <v>50</v>
       </c>
+      <c r="C1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">

--- a/xlsx/HerbalNames.xlsx
+++ b/xlsx/HerbalNames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hadle\Documents\GitHub\voynichTEI\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8854C489-692C-49B4-850C-4C0FC1BCDEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB26D0FC-0093-4AE1-8144-D7277F21A44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E74B4125-5874-4082-9055-372A93C35FC0}"/>
+    <workbookView xWindow="-108" yWindow="672" windowWidth="11664" windowHeight="11952" xr2:uid="{E74B4125-5874-4082-9055-372A93C35FC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
